--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Note.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Note.xlsx
@@ -184,16 +184,16 @@
     <t xml:space="preserve">hotspring_meditation</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.27 fix 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">온천에서 명상하면 몸도 마음도 후끈후끈</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hot spring meditation will warm you from the inside out!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">温泉で瞑想すれば、心も体もほっこり</t>
+    <t xml:space="preserve">EA 23.247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">온천에서 「휴식」하면 몸도 마음도 후끈후끈</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Take a "Rest" at the hot spring to warm you from the inside out!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">温泉で「休憩」すれば、心も体もほっこり</t>
   </si>
   <si>
     <t xml:space="preserve">pond_carp</t>
@@ -221,7 +221,7 @@
   <fonts count="4">
     <font>
       <sz val="10"/>
-      <name val="나눔고딕"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
     </font>
@@ -438,9 +438,11 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultColWidth="7.9609375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.62109375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="14.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="16.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="16.15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Note.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Note.xlsx
@@ -35,7 +35,7 @@
     <t xml:space="preserve">palmia_barrack</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.252</t>
+    <t xml:space="preserve">EA 23.260</t>
   </si>
   <si>
     <t xml:space="preserve">Palmian Royal Officers' Quarters</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Note.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Note.xlsx
@@ -35,7 +35,7 @@
     <t xml:space="preserve">palmia_barrack</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.260</t>
+    <t xml:space="preserve">EA 23.267</t>
   </si>
   <si>
     <t xml:space="preserve">Palmian Royal Officers' Quarters</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Note.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Note.xlsx
@@ -35,7 +35,7 @@
     <t xml:space="preserve">palmia_barrack</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.267</t>
+    <t xml:space="preserve">EA 23.281</t>
   </si>
   <si>
     <t xml:space="preserve">Palmian Royal Officers' Quarters</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Note.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Note.xlsx
@@ -35,7 +35,7 @@
     <t xml:space="preserve">palmia_barrack</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.281</t>
+    <t xml:space="preserve">EA 23.282 Patch 2</t>
   </si>
   <si>
     <t xml:space="preserve">Palmian Royal Officers' Quarters</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Note.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Note.xlsx
@@ -35,7 +35,7 @@
     <t xml:space="preserve">palmia_barrack</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.282 Patch 2</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">Palmian Royal Officers' Quarters</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Note.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Note.xlsx
@@ -35,7 +35,7 @@
     <t xml:space="preserve">palmia_barrack</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.287</t>
+    <t xml:space="preserve">EA 23.295</t>
   </si>
   <si>
     <t xml:space="preserve">Palmian Royal Officers' Quarters</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Note.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Note.xlsx
@@ -35,7 +35,7 @@
     <t xml:space="preserve">palmia_barrack</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.295</t>
+    <t xml:space="preserve">EA 23.307</t>
   </si>
   <si>
     <t xml:space="preserve">Palmian Royal Officers' Quarters</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Note.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Note.xlsx
@@ -35,7 +35,7 @@
     <t xml:space="preserve">palmia_barrack</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.307</t>
+    <t xml:space="preserve">EA 23.325</t>
   </si>
   <si>
     <t xml:space="preserve">Palmian Royal Officers' Quarters</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Note.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Note.xlsx
@@ -35,7 +35,7 @@
     <t xml:space="preserve">palmia_barrack</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.325</t>
+    <t xml:space="preserve">EA 23.338 Patch 2</t>
   </si>
   <si>
     <t xml:space="preserve">Palmian Royal Officers' Quarters</t>
